--- a/比特配置文件.xlsx
+++ b/比特配置文件.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="22060"/>
+    <workbookView windowWidth="21480" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="138">
   <si>
     <t>窗口ID</t>
   </si>
@@ -285,7 +285,7 @@
     <t>b1127c7a20bd4952bbc06c41e1b226c5</t>
   </si>
   <si>
-    <t>钱程似锦4</t>
+    <t>前程似锦4</t>
   </si>
   <si>
     <t>00287da1c0964c6889a239c98547b0f5</t>
@@ -1404,12 +1404,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:E66"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="54.4423076923077" customWidth="1"/>
+    <col min="1" max="1" width="54.4416666666667" customWidth="1"/>
     <col min="2" max="2" width="15.625" customWidth="1"/>
     <col min="3" max="3" width="25.75" customWidth="1"/>
-    <col min="4" max="4" width="31.0288461538462" customWidth="1"/>
+    <col min="4" max="4" width="31.0333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1" spans="1:5">
@@ -1852,7 +1852,9 @@
       <c r="B31" t="s">
         <v>67</v>
       </c>
-      <c r="C31"/>
+      <c r="C31" t="s">
+        <v>15</v>
+      </c>
       <c r="D31" t="s">
         <v>16</v>
       </c>
@@ -1867,7 +1869,9 @@
       <c r="B32" t="s">
         <v>69</v>
       </c>
-      <c r="C32"/>
+      <c r="C32" t="s">
+        <v>15</v>
+      </c>
       <c r="D32" t="s">
         <v>16</v>
       </c>
@@ -1882,7 +1886,9 @@
       <c r="B33" t="s">
         <v>71</v>
       </c>
-      <c r="C33"/>
+      <c r="C33" t="s">
+        <v>15</v>
+      </c>
       <c r="D33" t="s">
         <v>16</v>
       </c>
@@ -1897,7 +1903,9 @@
       <c r="B34" t="s">
         <v>73</v>
       </c>
-      <c r="C34"/>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
       <c r="D34" t="s">
         <v>16</v>
       </c>
@@ -1912,7 +1920,9 @@
       <c r="B35" t="s">
         <v>75</v>
       </c>
-      <c r="C35"/>
+      <c r="C35" t="s">
+        <v>15</v>
+      </c>
       <c r="D35" t="s">
         <v>16</v>
       </c>
@@ -1961,7 +1971,9 @@
       <c r="B38" t="s">
         <v>81</v>
       </c>
-      <c r="C38"/>
+      <c r="C38" t="s">
+        <v>15</v>
+      </c>
       <c r="D38" t="s">
         <v>16</v>
       </c>
@@ -1993,7 +2005,9 @@
       <c r="B40" t="s">
         <v>85</v>
       </c>
-      <c r="C40"/>
+      <c r="C40" t="s">
+        <v>15</v>
+      </c>
       <c r="D40" t="s">
         <v>16</v>
       </c>
@@ -2008,7 +2022,9 @@
       <c r="B41" t="s">
         <v>87</v>
       </c>
-      <c r="C41"/>
+      <c r="C41" t="s">
+        <v>15</v>
+      </c>
       <c r="D41" t="s">
         <v>16</v>
       </c>
@@ -2044,7 +2060,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="44" ht="17.6" spans="1:5">
+    <row r="44" ht="14.25" spans="1:5">
       <c r="A44" s="1" t="s">
         <v>92</v>
       </c>
@@ -2079,7 +2095,9 @@
       <c r="B46" t="s">
         <v>97</v>
       </c>
-      <c r="C46"/>
+      <c r="C46" t="s">
+        <v>15</v>
+      </c>
       <c r="D46" t="s">
         <v>16</v>
       </c>
@@ -2319,9 +2337,6 @@
       <c r="B62" t="s">
         <v>129</v>
       </c>
-      <c r="C62" t="s">
-        <v>15</v>
-      </c>
       <c r="D62" t="s">
         <v>16</v>
       </c>
@@ -2336,9 +2351,6 @@
       <c r="B63" t="s">
         <v>131</v>
       </c>
-      <c r="C63" t="s">
-        <v>15</v>
-      </c>
       <c r="D63" t="s">
         <v>16</v>
       </c>
@@ -2353,9 +2365,6 @@
       <c r="B64" t="s">
         <v>133</v>
       </c>
-      <c r="C64" t="s">
-        <v>15</v>
-      </c>
       <c r="D64" t="s">
         <v>16</v>
       </c>
@@ -2370,9 +2379,6 @@
       <c r="B65" t="s">
         <v>135</v>
       </c>
-      <c r="C65" t="s">
-        <v>15</v>
-      </c>
       <c r="D65" t="s">
         <v>16</v>
       </c>
@@ -2386,9 +2392,6 @@
       </c>
       <c r="B66" t="s">
         <v>137</v>
-      </c>
-      <c r="C66" t="s">
-        <v>15</v>
       </c>
       <c r="D66" t="s">
         <v>16</v>
@@ -2411,9 +2414,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="8.61538461538461" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="8.61666666666667" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="3"/>
   <sheetData>
-    <row r="1" ht="17.6" spans="1:4">
+    <row r="1" ht="14.25" spans="1:4">
       <c r="A1" t="s">
         <v>94</v>
       </c>
@@ -2424,7 +2427,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" ht="17.6" spans="1:4">
+    <row r="2" ht="14.25" spans="1:4">
       <c r="A2" t="s">
         <v>90</v>
       </c>
